--- a/artfynd/A 51198-2022 artfynd.xlsx
+++ b/artfynd/A 51198-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 51198-2022 artfynd.xlsx
+++ b/artfynd/A 51198-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>151261</v>
       </c>
       <c r="B2" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>755082.1635472927</v>
+        <v>755082</v>
       </c>
       <c r="R2" t="n">
-        <v>7085027.371313165</v>
+        <v>7085027</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2011-08-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2011-08-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,16 +775,11 @@
         <v>6932856</v>
       </c>
       <c r="B3" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>754558.179242464</v>
+        <v>754558</v>
       </c>
       <c r="R3" t="n">
-        <v>7084864.513930657</v>
+        <v>7084865</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2013-09-08</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2013-09-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,37 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6993813</v>
+        <v>6993797</v>
       </c>
       <c r="B4" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>754709.2685123025</v>
+        <v>754626</v>
       </c>
       <c r="R4" t="n">
-        <v>7084946.459153497</v>
+        <v>7084870</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,19 +942,9 @@
           <t>2013-10-13</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2013-10-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,37 +976,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6993815</v>
+        <v>6993814</v>
       </c>
       <c r="B5" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>754734.4789527033</v>
+        <v>754729</v>
       </c>
       <c r="R5" t="n">
-        <v>7084936.969781956</v>
+        <v>7084939</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,19 +1044,9 @@
           <t>2013-10-13</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2013-10-13</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,37 +1078,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6993816</v>
+        <v>6993817</v>
       </c>
       <c r="B6" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1178,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>754736.4954853345</v>
+        <v>754738</v>
       </c>
       <c r="R6" t="n">
-        <v>7084934.027266744</v>
+        <v>7084959</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,19 +1146,9 @@
           <t>2013-10-13</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2013-10-13</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6993814</v>
+        <v>54902987</v>
       </c>
       <c r="B7" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,34 +1191,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Röbäcksskogen: Jättstuguberget, Vb</t>
+          <t>Röbäcksskogen, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>754728.5611421557</v>
+        <v>754800</v>
       </c>
       <c r="R7" t="n">
-        <v>7084938.707727573</v>
+        <v>7084983</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,22 +1245,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2013-10-13</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-08-20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2013-10-13</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-08-20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,11 +1261,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>äldre barrskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1372,50 +1277,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>6993810</v>
+        <v>54902990</v>
       </c>
       <c r="B8" t="n">
-        <v>90649</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4363</v>
+        <v>4361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Röbäcksskogen: Jättstuguberget, Vb</t>
+          <t>Röbäcksskogen, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>754678.8113378173</v>
+        <v>754775</v>
       </c>
       <c r="R8" t="n">
-        <v>7084911.145531745</v>
+        <v>7084970</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,22 +1342,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2013-10-13</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-08-20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2013-10-13</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-08-20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,11 +1358,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>äldre barrskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1489,15 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>6993797</v>
+        <v>54902991</v>
       </c>
       <c r="B9" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1505,34 +1385,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Röbäcksskogen: Jättstuguberget, Vb</t>
+          <t>Röbäcksskogen, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>754626.197844327</v>
+        <v>754775</v>
       </c>
       <c r="R9" t="n">
-        <v>7084869.594393166</v>
+        <v>7084963</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,22 +1439,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2013-10-13</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-08-20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2013-10-13</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-08-20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,11 +1455,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>äldre barrskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1606,15 +1471,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>6993812</v>
+        <v>54902995</v>
       </c>
       <c r="B10" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1622,34 +1482,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Röbäcksskogen: Jättstuguberget, Vb</t>
+          <t>Röbäcksskogen, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>754712.6220216659</v>
+        <v>754768</v>
       </c>
       <c r="R10" t="n">
-        <v>7084932.531057524</v>
+        <v>7084910</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1676,22 +1536,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2013-10-13</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-08-20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2013-10-13</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-08-20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,11 +1552,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>äldre barrskog</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1723,15 +1568,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>54902994</v>
+        <v>54902996</v>
       </c>
       <c r="B11" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1739,21 +1579,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1763,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>754763.6395518461</v>
+        <v>754763</v>
       </c>
       <c r="R11" t="n">
-        <v>7084917.151061076</v>
+        <v>7084904</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1796,19 +1636,9 @@
           <t>2015-08-20</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2015-08-20</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1835,15 +1665,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>54902991</v>
+        <v>54902997</v>
       </c>
       <c r="B12" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,10 +1700,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>754774.9936572184</v>
+        <v>754742</v>
       </c>
       <c r="R12" t="n">
-        <v>7084963.338396526</v>
+        <v>7084883</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1908,19 +1733,9 @@
           <t>2015-08-20</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2015-08-20</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1947,15 +1762,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>54902995</v>
+        <v>55076705</v>
       </c>
       <c r="B13" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1987,10 +1797,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>754767.8160226613</v>
+        <v>754562</v>
       </c>
       <c r="R13" t="n">
-        <v>7084909.502573671</v>
+        <v>7084881</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2017,22 +1827,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2015-08-20</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-09-06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2015-08-20</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-09-06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2059,15 +1859,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>54902996</v>
+        <v>55076708</v>
       </c>
       <c r="B14" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2099,10 +1894,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>754762.9128560078</v>
+        <v>754540</v>
       </c>
       <c r="R14" t="n">
-        <v>7084904.222559957</v>
+        <v>7084912</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2129,22 +1924,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2015-08-20</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-09-06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2015-08-20</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-09-06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2171,37 +1956,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>54902992</v>
+        <v>54902989</v>
       </c>
       <c r="B15" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2211,10 +1991,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>754782.3333187889</v>
+        <v>754775</v>
       </c>
       <c r="R15" t="n">
-        <v>7084938.640143861</v>
+        <v>7084966</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2244,19 +2024,9 @@
           <t>2015-08-20</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2015-08-20</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2283,15 +2053,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>55076705</v>
+        <v>54902994</v>
       </c>
       <c r="B16" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2299,21 +2064,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2323,10 +2088,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>754562.1877472842</v>
+        <v>754764</v>
       </c>
       <c r="R16" t="n">
-        <v>7084880.81530831</v>
+        <v>7084917</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2353,22 +2118,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2015-09-06</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-08-20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2015-09-06</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-08-20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2395,15 +2150,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>55076706</v>
+        <v>6993810</v>
       </c>
       <c r="B17" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93193</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2411,34 +2161,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>4363</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Röbäcksskogen, Vb</t>
+          <t>Röbäcksskogen: Jättstuguberget, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>754543.0024539579</v>
+        <v>754679</v>
       </c>
       <c r="R17" t="n">
-        <v>7084903.66477577</v>
+        <v>7084911</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2465,22 +2215,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2015-09-06</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-10-13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2015-09-06</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-10-13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2491,6 +2231,11 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>äldre barrskog</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2507,15 +2252,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>68474139</v>
+        <v>6993818</v>
       </c>
       <c r="B18" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2523,21 +2263,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2547,10 +2287,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>754696.0401533209</v>
+        <v>754763</v>
       </c>
       <c r="R18" t="n">
-        <v>7084901.451029581</v>
+        <v>7084976</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2577,22 +2317,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2017-11-26</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-10-13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2017-11-26</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-10-13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2604,9 +2334,9 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>gran</t>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>äldre barrskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2621,6 +2351,1523 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>54902988</v>
+      </c>
+      <c r="B19" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Röbäcksskogen, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>754772</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7084968</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2015-08-20</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2015-08-20</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>54902992</v>
+      </c>
+      <c r="B20" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Röbäcksskogen, Vb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>754782</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7084939</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2015-08-20</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2015-08-20</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>55076703</v>
+      </c>
+      <c r="B21" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Röbäcksskogen, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>754569</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7084840</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2015-09-06</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2015-09-06</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>55076706</v>
+      </c>
+      <c r="B22" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Röbäcksskogen, Vb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>754543</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7084904</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2015-09-06</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2015-09-06</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>6993815</v>
+      </c>
+      <c r="B23" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Röbäcksskogen: Jättstuguberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>754734</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7084937</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2013-10-13</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2013-10-13</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>6993796</v>
+      </c>
+      <c r="B24" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Röbäcksskogen: Jättstuguberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>754557</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7084928</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2013-10-13</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2013-10-13</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>6993812</v>
+      </c>
+      <c r="B25" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Röbäcksskogen: Jättstuguberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>754713</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7084933</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2013-10-13</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2013-10-13</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>6993813</v>
+      </c>
+      <c r="B26" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Röbäcksskogen: Jättstuguberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>754709</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7084946</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2013-10-13</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2013-10-13</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>6993816</v>
+      </c>
+      <c r="B27" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Röbäcksskogen, Vb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>754736</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7084934</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2013-10-13</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2013-10-13</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>6993819</v>
+      </c>
+      <c r="B28" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Röbäcksskogen, Vb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>754782</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7084979</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2013-10-13</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2013-10-13</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>16859685</v>
+      </c>
+      <c r="B29" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Röbäcksskogen, Vb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>754586</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7084924</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2014-11-21</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2014-11-21</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>äldre tallskog</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>16859686</v>
+      </c>
+      <c r="B30" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Röbäcksskogen, Vb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>754562</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7084929</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2014-11-21</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2014-11-21</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>äldre tallskog</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>103262267</v>
+      </c>
+      <c r="B31" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Röbäck, Vb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>754656</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7084872</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Lars Karlsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Lars Karlsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>68474139</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Röbäcksskogen, Vb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>754696</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7084901</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2017-11-26</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2017-11-26</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>79265843</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Jättstuberget, Röbäck, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>754599</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7084943</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2019-08-05</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2019-08-05</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Marcus Östman</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Marcus Östman</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51198-2022 artfynd.xlsx
+++ b/artfynd/A 51198-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AZ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/151261</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6932856</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6993797</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6993814</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6993817</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,6 +1304,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54902987</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1371,6 +1406,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54902990</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1468,6 +1508,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54902991</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1565,6 +1610,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54902995</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1662,6 +1712,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54902996</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1759,6 +1814,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54902997</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1856,6 +1916,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55076705</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1953,6 +2018,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55076708</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2050,6 +2120,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54902989</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2147,6 +2222,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54902994</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2249,6 +2329,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6993810</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2351,6 +2436,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6993818</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2448,6 +2538,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54902988</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2545,6 +2640,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54902992</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2642,6 +2742,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55076703</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2739,6 +2844,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55076706</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2841,6 +2951,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6993815</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2943,6 +3058,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6993796</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3045,6 +3165,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6993812</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3147,6 +3272,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6993813</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3249,6 +3379,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6993816</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3351,6 +3486,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6993819</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3453,6 +3593,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16859685</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3555,6 +3700,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16859686</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3657,6 +3807,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103262267</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3759,6 +3914,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68474139</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3868,8 +4028,47 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79265843</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>